--- a/data/trending_integrated_20261006_12.xlsx
+++ b/data/trending_integrated_20261006_12.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52630737290</v>
+        <v>52645061300</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47700</v>
+        <v>17980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.92%</t>
+          <t>'+17.06%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>609</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>381</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>3523</v>
+        <v>71</v>
       </c>
       <c r="H3" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K3" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L3" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M3" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N3" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>226003292475</v>
+        <v>94202511625</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R3" t="n">
-        <v>477000</v>
+        <v>41000</v>
       </c>
       <c r="S3" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 美 FDA 승인 기대감 고조. VAI 공시 및 블로그 통해 결과 확인, 로슈 제치고 간암 치료제 시장 선도 전망.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', 'VAI']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17960</v>
+        <v>47350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.93%</t>
+          <t>'+17.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>620</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>382</v>
       </c>
       <c r="G4" t="n">
-        <v>71</v>
+        <v>3680</v>
       </c>
       <c r="H4" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K4" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L4" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M4" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>93315103120</v>
+        <v>226783737550</v>
       </c>
       <c r="P4" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>41000</v>
+        <v>477000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>HLB 간암 신약 FDA 승인 기대감 및 VAI 관련 긍정적 블로그 내용 확산. 동진 결과 발표 임박 및 로슈와의 비교 우위 언급. 상승 추세 전망 및 80만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA', '간암 신약', 'VAI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4910</v>
+        <v>4905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.59%</t>
+          <t>'+11.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>120262670594</v>
+        <v>121145641834</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20550</v>
+        <v>3095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.37%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E6" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K6" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L6" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M6" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>126789208715</v>
+        <v>39812462264</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>-64000</v>
+        <v>-8000</v>
       </c>
       <c r="S6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보안 관련 정부 점검 지시에 따른 보안주 상승 기대감. 엑스게이트는 금융 고객사 207곳 보유.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', '금융고객사', '정부점검']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3105</v>
+        <v>20400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.14%</t>
+          <t>'+8.57%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2845</v>
+        <v>18790</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>21400</v>
       </c>
       <c r="L7" t="n">
-        <v>3360</v>
+        <v>22300</v>
       </c>
       <c r="M7" t="n">
-        <v>2995</v>
+        <v>20050</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>38996053036</v>
+        <v>127549125965</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-8000</v>
+        <v>-64000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>보안 관련 정부 점검 지시에 따른 보안주 상승 기대감. 엑스게이트는 금융 고객사 207곳 보유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['보안주', '금융고객사', '정부점검']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.76%</t>
+          <t>'+8.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H8" t="n">
         <v>1.09</v>
@@ -1162,7 +1162,7 @@
         <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>19107218127</v>
+        <v>19170745599</v>
       </c>
       <c r="P8" t="n">
         <v>2970</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18350</v>
+        <v>18320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.09%</t>
+          <t>'+2.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>694</v>
+        <v>716</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>191128895755</v>
+        <v>192984159490</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 등의 상승 언급. 3분기 영업이익 증가 및 현재 가격대 매물 소화 과정을 근거로 제시하며 상승 기대감 표출.</t>
+          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 급등에 따른 대한광통신 기대감 고조. 3분기 영업이익 증가 및 매물대 소화 후 상승 전망. 프로그램 매수세 유입 및 공매도 이슈 부각.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '매물대']</t>
+          <t>['광통신', '매물대', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15810</v>
+        <v>15710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.00%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H10" t="n">
         <v>0.32</v>
@@ -1346,7 +1346,7 @@
         <v>0.18</v>
       </c>
       <c r="O10" t="n">
-        <v>53622836810</v>
+        <v>55797047175</v>
       </c>
       <c r="P10" t="n">
         <v>29750</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집 및 통신 광원 반도체 기술 보유. 회사 차원 공식 발표는 부재.</t>
+          <t>기타법인의 350만주 자사주 매집에 따른 저평가 및 상승 기대감 존재. 다만, 회사 뉴스 부재 및 자본잠식 이슈, 일부 매도 의견 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주 매집', '광통신', '반도체']</t>
+          <t>['자사주', '저평가', '자본잠식']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17750</v>
+        <v>17770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>43354939840</v>
+        <v>44228194665</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>271750</v>
+        <v>271250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.54%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>771</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="G12" t="n">
-        <v>2553</v>
+        <v>2569</v>
       </c>
       <c r="H12" t="n">
         <v>46.41</v>
@@ -1524,13 +1524,13 @@
         <v>279000</v>
       </c>
       <c r="M12" t="n">
-        <v>271500</v>
+        <v>271000</v>
       </c>
       <c r="N12" t="n">
         <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>1706163262750</v>
+        <v>1773036557750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 시장 급등 랠리 및 엔비디아 신고가 경신 등 호재 언급. 다만, 마이크론 하락 및 감정적 기대감 위주의 내용으로 fact_score는 보수적으로 산정.</t>
+          <t>반도체 시장 랠리 및 엔비디아 신고가 경신 속 삼성전자 30만 재돌파 기대감. 외국인 매수세 유입 전망. 단, 미 메모리 반도체 하락 및 마이크론 주가 하락 등 일부 부정적 지표도 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '엔비디아', '영업이익']</t>
+          <t>['반도체', '외국인', '엔비디아']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1789000</v>
+        <v>1787000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="G13" t="n">
-        <v>1793</v>
+        <v>1834</v>
       </c>
       <c r="H13" t="n">
         <v>49.76</v>
@@ -1622,7 +1622,7 @@
         <v>49.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2318642860500</v>
+        <v>2382022645500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>오너리스크 및 솔리다임 상장 이슈로 인한 SK하이닉스 주가 하락 우려. HBM 경쟁력 약화 지적.</t>
+          <t>SK하이닉스 오너 리스크(최태원 관련 이슈) 및 HBM 경쟁력 약화, 솔리다임 상장 관련 부정적 전망. 국장 악재 및 외국인 매도세 지속으로 인한 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['오너리스크', '솔리다임', 'HBM']</t>
+          <t>['오너 리스크', 'HBM', '솔리다임']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261006_12.xlsx
+++ b/data/trending_integrated_20261006_12.xlsx
@@ -584,7 +584,7 @@
         <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52645061300</v>
+        <v>52650382390</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17980</v>
+        <v>17950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.06%</t>
+          <t>'+16.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -702,7 +702,7 @@
         <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>94202511625</v>
+        <v>94960444295</v>
       </c>
       <c r="P3" t="n">
         <v>38400</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47350</v>
+        <v>47200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.06%</t>
+          <t>'+16.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="F4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G4" t="n">
-        <v>3680</v>
+        <v>3794</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>226783737550</v>
+        <v>227905703400</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 FDA 승인 기대감 및 VAI 관련 긍정적 블로그 내용 확산. 동진 결과 발표 임박 및 로슈와의 비교 우위 언급. 상승 추세 전망 및 80만원 목표가 제시.</t>
+          <t>HLB 간암 신약 FDA 승인 관련 긍정적 전망 다수. VAI 등장 및 동진 S&amp;T 결과에 대한 기대감, 리보세라닙 완제의약품 제조시설 FDA 실사 결과 공시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA', '간암 신약', 'VAI']</t>
+          <t>['FDA 승인', '간암 신약', '리보세라닙']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4905</v>
+        <v>4960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.48%</t>
+          <t>'+12.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>121145641834</v>
+        <v>122852286203</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3095</v>
+        <v>20600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.79%</t>
+          <t>'+9.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2845</v>
+        <v>18790</v>
       </c>
       <c r="K6" t="n">
-        <v>3200</v>
+        <v>21400</v>
       </c>
       <c r="L6" t="n">
-        <v>3360</v>
+        <v>22300</v>
       </c>
       <c r="M6" t="n">
-        <v>2995</v>
+        <v>20050</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>39812462264</v>
+        <v>128974593140</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>-8000</v>
+        <v>-64000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>보안 관련 정부 점검 지시에 따른 보안주 상승 기대감. 엑스게이트는 금융 고객사 207곳 보유.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['보안주', '금융고객사', '정부점검']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20400</v>
+        <v>3100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.57%</t>
+          <t>'+8.96%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K7" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L7" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M7" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>127549125965</v>
+        <v>40607998335</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>-64000</v>
+        <v>-8000</v>
       </c>
       <c r="S7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안 관련 정부 점검 지시에 따른 보안주 상승 기대감. 엑스게이트는 금융 고객사 207곳 보유.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '금융고객사', '정부점검']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1450</v>
+        <v>1435</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.21%</t>
+          <t>'+7.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H8" t="n">
         <v>1.09</v>
@@ -1162,7 +1162,7 @@
         <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>19170745599</v>
+        <v>19316631914</v>
       </c>
       <c r="P8" t="n">
         <v>2970</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18320</v>
+        <v>18360</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.92%</t>
+          <t>'+3.15%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>192984159490</v>
+        <v>194373968350</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 급등에 따른 대한광통신 기대감 고조. 3분기 영업이익 증가 및 매물대 소화 후 상승 전망. 프로그램 매수세 유입 및 공매도 이슈 부각.</t>
+          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 급등에 따른 기대감. 3분기 영업이익 약 65억 확인, 매물 소화 후 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '매물대', '공매도']</t>
+          <t>['광통신', '영업이익', '매물 소화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15710</v>
+        <v>15570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+1.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="H10" t="n">
         <v>0.32</v>
@@ -1346,7 +1346,7 @@
         <v>0.18</v>
       </c>
       <c r="O10" t="n">
-        <v>55797047175</v>
+        <v>57568959755</v>
       </c>
       <c r="P10" t="n">
         <v>29750</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기타법인의 350만주 자사주 매집에 따른 저평가 및 상승 기대감 존재. 다만, 회사 뉴스 부재 및 자본잠식 이슈, 일부 매도 의견 혼재.</t>
+          <t>기타법인 350만주 자사주 매집 확인. 초저평가 및 통신 광원 반도체 독보적 기술 보유 언급되나, 자본잠식 및 회사 무대응에 대한 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주', '저평가', '자본잠식']</t>
+          <t>['자사주', '자본잠식', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17770</v>
+        <v>17800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.91%</t>
+          <t>'+1.08%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>44228194665</v>
+        <v>44997601200</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>271250</v>
+        <v>271000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="G12" t="n">
-        <v>2569</v>
+        <v>2203</v>
       </c>
       <c r="H12" t="n">
         <v>46.41</v>
@@ -1530,7 +1530,7 @@
         <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>1773036557750</v>
+        <v>1819417323500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 시장 랠리 및 엔비디아 신고가 경신 속 삼성전자 30만 재돌파 기대감. 외국인 매수세 유입 전망. 단, 미 메모리 반도체 하락 및 마이크론 주가 하락 등 일부 부정적 지표도 존재.</t>
+          <t>외국인 매수 및 자사주 취득 마무리 속 3분기 영업이익 100조 전망. 다만, 실적 추정치 대비 목표주가 도달 가능성에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '엔비디아']</t>
+          <t>['영업이익', '자사주', '목표주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G13" t="n">
-        <v>1834</v>
+        <v>1854</v>
       </c>
       <c r="H13" t="n">
         <v>49.76</v>
@@ -1622,7 +1622,7 @@
         <v>49.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2382022645500</v>
+        <v>2439026818500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>

--- a/data/trending_integrated_20261006_12.xlsx
+++ b/data/trending_integrated_20261006_12.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52650382390</v>
+        <v>52659255210</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17950</v>
+        <v>18020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.86%</t>
+          <t>'+17.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H3" t="n">
         <v>2.17</v>
@@ -702,7 +702,7 @@
         <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>94960444295</v>
+        <v>95886770070</v>
       </c>
       <c r="P3" t="n">
         <v>38400</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47200</v>
+        <v>47350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.69%</t>
+          <t>'+17.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G4" t="n">
-        <v>3794</v>
+        <v>3911</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>227905703400</v>
+        <v>229307068300</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -860,7 +860,7 @@
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>122852286203</v>
+        <v>123739005988</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20600</v>
+        <v>3135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.63%</t>
+          <t>'+10.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K6" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L6" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M6" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>128974593140</v>
+        <v>41649164893</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>-64000</v>
+        <v>-8000</v>
       </c>
       <c r="S6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보안 관련 정부 점검 지시에 따른 보안주 상승 기대감. 엑스게이트는 금융 고객사 207곳 보유.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', '금융고객사', '정부점검']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3100</v>
+        <v>20700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.96%</t>
+          <t>'+10.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2845</v>
+        <v>18790</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>21400</v>
       </c>
       <c r="L7" t="n">
-        <v>3360</v>
+        <v>22300</v>
       </c>
       <c r="M7" t="n">
-        <v>2995</v>
+        <v>20050</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>40607998335</v>
+        <v>130434117315</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-8000</v>
+        <v>-64000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>금융권 보안 위협 증가에 따른 보안주 상승 기대감. 양자 보안 기술 보유 기업 주목.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['보안주', '양자 보안', '금융권']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.09%</t>
+          <t>'+7.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
         <v>1.09</v>
@@ -1162,7 +1162,7 @@
         <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>19316631914</v>
+        <v>19382078990</v>
       </c>
       <c r="P8" t="n">
         <v>2970</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18360</v>
+        <v>18370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.15%</t>
+          <t>'+3.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>743</v>
+        <v>697</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>194373968350</v>
+        <v>195681098105</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 급등에 따른 기대감. 3분기 영업이익 약 65억 확인, 매물 소화 후 상승 추세 전망.</t>
+          <t>미국 광통신 섹터 강세와 함께 3분기 영업이익 증가. 매물대 소화 후 전고점 돌파 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '매물 소화']</t>
+          <t>['광통신', '영업이익', '매물대 소화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15570</v>
+        <v>17810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.43%</t>
+          <t>'+1.14%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>256</v>
+        <v>399</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>15350</v>
+        <v>17610</v>
       </c>
       <c r="K10" t="n">
-        <v>14920</v>
+        <v>17700</v>
       </c>
       <c r="L10" t="n">
-        <v>16590</v>
+        <v>18160</v>
       </c>
       <c r="M10" t="n">
-        <v>14300</v>
+        <v>17630</v>
       </c>
       <c r="N10" t="n">
-        <v>0.18</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>57568959755</v>
+        <v>46733995410</v>
       </c>
       <c r="P10" t="n">
-        <v>29750</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>12760</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>14000</v>
+        <v>381000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-45000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기타법인 350만주 자사주 매집 확인. 초저평가 및 통신 광원 반도체 독보적 기술 보유 언급되나, 자본잠식 및 회사 무대응에 대한 우려.</t>
+          <t>주택 공급 확대 기사에도 불구하고, 원전 테마 언급 및 주가 누르기 의혹 제기로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주', '자본잠식', '반도체']</t>
+          <t>['주택 공급', '원전 테마', '허매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17800</v>
+        <v>15350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.08%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>405</v>
+        <v>281</v>
       </c>
       <c r="H11" t="n">
-        <v>9.390000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17610</v>
+        <v>15350</v>
       </c>
       <c r="K11" t="n">
-        <v>17700</v>
+        <v>14920</v>
       </c>
       <c r="L11" t="n">
-        <v>18160</v>
+        <v>16590</v>
       </c>
       <c r="M11" t="n">
-        <v>17630</v>
+        <v>14300</v>
       </c>
       <c r="N11" t="n">
-        <v>9.449999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="O11" t="n">
-        <v>44997601200</v>
+        <v>59564810970</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>29750</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>12760</v>
       </c>
       <c r="R11" t="n">
-        <v>381000</v>
+        <v>14000</v>
       </c>
       <c r="S11" t="n">
-        <v>-45000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주택 공급 확대 기사에도 불구하고, 원전 테마 언급 및 주가 누르기 의혹 제기로 인한 투자 심리 위축.</t>
+          <t>기타법인 자사주 매집 후 급락 패턴 반복. 회사 무대응 및 자본잠식 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주택 공급', '원전 테마', '허매도']</t>
+          <t>['자사주 매집', '자본잠식', '패턴 반복']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>271000</v>
+        <v>271500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G12" t="n">
-        <v>2203</v>
+        <v>1880</v>
       </c>
       <c r="H12" t="n">
         <v>46.41</v>
@@ -1530,7 +1530,7 @@
         <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>1819417323500</v>
+        <v>1863077946750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외국인 매수 및 자사주 취득 마무리 속 3분기 영업이익 100조 전망. 다만, 실적 추정치 대비 목표주가 도달 가능성에 대한 의문 제기.</t>
+          <t>3분기 실적 전망 하향 조정 가능성 속 자사주 매입 마무리. 목표 주가 60만원 달성 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주', '목표주가']</t>
+          <t>['자사주 매입', '실적 전망', '목표 주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1787000</v>
+        <v>1786000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.93%</t>
+          <t>'-2.99%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G13" t="n">
-        <v>1854</v>
+        <v>1916</v>
       </c>
       <c r="H13" t="n">
         <v>49.76</v>
@@ -1616,13 +1616,13 @@
         <v>1837000</v>
       </c>
       <c r="M13" t="n">
-        <v>1786000</v>
+        <v>1785000</v>
       </c>
       <c r="N13" t="n">
         <v>49.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2439026818500</v>
+        <v>2493213591500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SK하이닉스 오너 리스크(최태원 관련 이슈) 및 HBM 경쟁력 약화, 솔리다임 상장 관련 부정적 전망. 국장 악재 및 외국인 매도세 지속으로 인한 주가 하락 우려.</t>
+          <t>오너 리스크 부각 속 HBM 시장 경쟁력 약화 우려. 솔리다임 상장 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261006_12.xlsx
+++ b/data/trending_integrated_20261006_12.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52659255210</v>
+        <v>52666892080</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18020</v>
+        <v>47400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.32%</t>
+          <t>'+17.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>644</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>389</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>3912</v>
       </c>
       <c r="H3" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K3" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L3" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M3" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N3" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>95886770070</v>
+        <v>230165778175</v>
       </c>
       <c r="P3" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
-        <v>41000</v>
+        <v>477000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>HLB 간암 신약 FDA 승인 관련 긍정적 전망 다수. VAI 등장 및 동진 S&amp;T 결과에 대한 기대감, 리보세라닙 완제의약품 제조시설 FDA 실사 결과 공시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA 승인', '간암 신약', '리보세라닙']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47350</v>
+        <v>17880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.06%</t>
+          <t>'+16.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>648</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>388</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>3911</v>
+        <v>74</v>
       </c>
       <c r="H4" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K4" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L4" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M4" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N4" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>229307068300</v>
+        <v>96552402755</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R4" t="n">
-        <v>477000</v>
+        <v>41000</v>
       </c>
       <c r="S4" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 FDA 승인 관련 긍정적 전망 다수. VAI 등장 및 동진 S&amp;T 결과에 대한 기대감, 리보세라닙 완제의약품 제조시설 FDA 실사 결과 공시.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', '리보세라닙']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4960</v>
+        <v>4990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.73%</t>
+          <t>'+13.41%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>123739005988</v>
+        <v>125556645251</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3135</v>
+        <v>3120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.19%</t>
+          <t>'+9.67%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H6" t="n">
         <v>1.82</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>41649164893</v>
+        <v>43394960368</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20700</v>
+        <v>20550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.16%</t>
+          <t>'+9.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
@@ -1070,7 +1070,7 @@
         <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>130434117315</v>
+        <v>132230135740</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>금융권 보안 위협 증가에 따른 보안주 상승 기대감. 양자 보안 기술 보유 기업 주목.</t>
+          <t>보안주로서 금융권 고객사 다수 보유, 은행 보안 문제와 연관된 상승 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '양자 보안', '금융권']</t>
+          <t>['보안주', '양자보안', '고객사']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+7.54%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
         <v>165</v>
@@ -1162,7 +1162,7 @@
         <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>19382078990</v>
+        <v>19442598316</v>
       </c>
       <c r="P8" t="n">
         <v>2970</v>
@@ -1222,13 +1222,13 @@
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>195681098105</v>
+        <v>196892624715</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세와 함께 3분기 영업이익 증가. 매물대 소화 후 전고점 돌파 기대감.</t>
+          <t>미국 증시 광통신 섹터 강세 및 3분기 영업이익 증가 추세. 매물 소화 후 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '매물대 소화']</t>
+          <t>['광통신', '영업이익', '매물소화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17810</v>
+        <v>17800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.14%</t>
+          <t>'+1.08%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>46733995410</v>
+        <v>47466605200</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15350</v>
+        <v>15340</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="H11" t="n">
         <v>0.32</v>
@@ -1438,7 +1438,7 @@
         <v>0.18</v>
       </c>
       <c r="O11" t="n">
-        <v>59564810970</v>
+        <v>62527060845</v>
       </c>
       <c r="P11" t="n">
         <v>29750</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G12" t="n">
-        <v>1880</v>
+        <v>1728</v>
       </c>
       <c r="H12" t="n">
         <v>46.41</v>
@@ -1530,7 +1530,7 @@
         <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>1863077946750</v>
+        <v>1889809462750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 전망 하향 조정 가능성 속 자사주 매입 마무리. 목표 주가 60만원 달성 기대감 존재.</t>
+          <t>3분기 실적 전망 100조 예상 속 자사주 취득 마무리, 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 매입', '실적 전망', '목표 주가']</t>
+          <t>['실적전망', '자사주매입', '주가하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1786000</v>
+        <v>1788000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.99%</t>
+          <t>'-2.88%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="G13" t="n">
-        <v>1916</v>
+        <v>1935</v>
       </c>
       <c r="H13" t="n">
         <v>49.76</v>
@@ -1622,7 +1622,7 @@
         <v>49.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2493213591500</v>
+        <v>2553093579000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>오너 리스크 부각 속 HBM 시장 경쟁력 약화 우려. 솔리다임 상장 관련 불확실성 존재.</t>
+          <t>하락 추세 속 오너 리스크 부각, 솔리다임 상장 관련 부정적 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['오너 리스크', 'HBM', '솔리다임']</t>
+          <t>['오너리스크', '솔리다임', '하락추세']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261006_12.xlsx
+++ b/data/trending_integrated_20261006_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52666892080</v>
+        <v>52672642500</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB의 간암 신약 미국 승인 신청 및 기타법인 대규모 자사주 매집으로 인한 2연상 기대감.</t>
+          <t>HLB 간암 신약 FDA 승인 관련 기대감. 기타법인 자사주 매집 및 유증 물량 소화.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['리보세라닙', '유증', '자사주']</t>
+          <t>['유증', '신약', '자사주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47400</v>
+        <v>17830</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.18%</t>
+          <t>'+16.08%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>644</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
-        <v>389</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>3912</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K3" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L3" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M3" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N3" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>230165778175</v>
+        <v>97566347725</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R3" t="n">
-        <v>477000</v>
+        <v>41000</v>
       </c>
       <c r="S3" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 FDA 승인 관련 긍정적 전망 다수. VAI 등장 및 동진 S&amp;T 결과에 대한 기대감, 리보세라닙 완제의약품 제조시설 FDA 실사 결과 공시.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', '리보세라닙']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17880</v>
+        <v>46900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.41%</t>
+          <t>'+15.95%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>652</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>392</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>4016</v>
       </c>
       <c r="H4" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K4" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L4" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M4" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>96552402755</v>
+        <v>231701563875</v>
       </c>
       <c r="P4" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>41000</v>
+        <v>477000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>미국 FDA 허가 기대감에 따른 상승 전망. VAI 긍정 신호 및 공매도 세력 대응.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA', '신약', 'VAI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4990</v>
+        <v>4975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.41%</t>
+          <t>'+13.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>125556645251</v>
+        <v>127131241061</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3120</v>
+        <v>3125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.67%</t>
+          <t>'+9.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.57</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H6" t="n">
         <v>1.82</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>43394960368</v>
+        <v>44521220547</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20550</v>
+        <v>20500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.37%</t>
+          <t>'+9.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
@@ -1070,7 +1070,7 @@
         <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>132230135740</v>
+        <v>133273841365</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안주로서 금융권 고객사 다수 보유, 은행 보안 문제와 연관된 상승 기대감.</t>
+          <t>은행 보안 강화 수혜 기대감. 금융 고객사 다수 보유 및 양자 보안 성장 가능성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '고객사']</t>
+          <t>['보안주', '양자보안', '금융고객사']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.54%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H8" t="n">
         <v>1.09</v>
@@ -1162,7 +1162,7 @@
         <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>19442598316</v>
+        <v>19487229705</v>
       </c>
       <c r="P8" t="n">
         <v>2970</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18370</v>
+        <v>18400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.20%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="n">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>196892624715</v>
+        <v>198143678675</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 3분기 영업이익 증가 추세. 매물 소화 후 상승 기대.</t>
+          <t>미국 광통신 섹터 강세와 함께 3분기 영업이익 증가. 매물대 소화 후 전고점 돌파 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '매물소화']</t>
+          <t>['광통신', '영업이익', '매물대 소화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17800</v>
+        <v>17750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.08%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>47466605200</v>
+        <v>48512371185</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15340</v>
+        <v>15360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F11" t="n">
         <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H11" t="n">
         <v>0.32</v>
@@ -1438,7 +1438,7 @@
         <v>0.18</v>
       </c>
       <c r="O11" t="n">
-        <v>62527060845</v>
+        <v>63716769460</v>
       </c>
       <c r="P11" t="n">
         <v>29750</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집 후 급락 패턴 반복. 회사 무대응 및 자본잠식 우려.</t>
+          <t>기타법인 자사주 매집에 따른 수급 기대감. 신규 상장 후 주가 변동성 관찰 필요.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주 매집', '자본잠식', '패턴 반복']</t>
+          <t>['자사주', '수급', '신규주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>271500</v>
+        <v>272000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="G12" t="n">
-        <v>1728</v>
+        <v>1660</v>
       </c>
       <c r="H12" t="n">
         <v>46.41</v>
@@ -1530,7 +1530,7 @@
         <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>1889809462750</v>
+        <v>1947219790000</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 전망 100조 예상 속 자사주 취득 마무리, 주가 하락에 대한 우려.</t>
+          <t>자사주 취득 마무리 후 수급 붕괴 우려. 3분기 실적 및 연말 전망 불확실.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적전망', '자사주매입', '주가하락']</t>
+          <t>['자사주', '수급', '실적']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1788000</v>
+        <v>19650</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.88%</t>
+          <t>'-1.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
-        <v>471</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>1935</v>
+        <v>259</v>
       </c>
       <c r="H13" t="n">
-        <v>49.76</v>
+        <v>27.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,58 +1607,150 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1841000</v>
+        <v>19960</v>
       </c>
       <c r="K13" t="n">
-        <v>1835000</v>
+        <v>20150</v>
       </c>
       <c r="L13" t="n">
-        <v>1837000</v>
+        <v>20150</v>
       </c>
       <c r="M13" t="n">
-        <v>1785000</v>
+        <v>19630</v>
       </c>
       <c r="N13" t="n">
-        <v>49.77</v>
+        <v>27.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2553093579000</v>
+        <v>31530449035</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>18440</v>
       </c>
       <c r="R13" t="n">
-        <v>-331000</v>
+        <v>-412000</v>
       </c>
       <c r="S13" t="n">
-        <v>38000</v>
+        <v>-26000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>하락 추세 속 오너 리스크 부각, 솔리다임 상장 관련 부정적 전망.</t>
+          <t>수주 기대감에도 불구하고 주가 부진. 브랜드 가치 활용 부족 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['오너리스크', '솔리다임', '하락추세']</t>
+          <t>['수주', '주가', '브랜드']</t>
         </is>
       </c>
       <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1789000</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-2.82%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>471</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1957</v>
+      </c>
+      <c r="H14" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1785000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2603945390500</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-331000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>38000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>오너 리스크 및 ADR 상장 관련 부정적 전망. 기업 실적 대비 주가 부진.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['오너리스크', 'ADR', '주가']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>6</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
